--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -682,22 +682,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>40.63</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -784,22 +787,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -816,22 +822,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -848,22 +857,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -880,22 +892,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -912,22 +927,25 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>15.91</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -944,22 +962,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>52.78</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -976,22 +997,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>37.84</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1075,22 +1099,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1107,22 +1134,25 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1139,22 +1169,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1171,22 +1204,25 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.1</v>
       </c>
       <c r="J19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1203,22 +1239,25 @@
         <v>28</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>17.86</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1235,22 +1274,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>17.65</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.5</v>
       </c>
       <c r="J21">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1267,22 +1309,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1509,22 +1554,25 @@
         <v>32</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5.9</v>
       </c>
       <c r="J29">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1541,22 +1589,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>86.11</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>13.89</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.9</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1573,22 +1624,25 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1800,22 +1854,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6.4</v>
       </c>
       <c r="J38">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1832,22 +1889,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>75.61</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>24.39</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.4</v>
       </c>
       <c r="J39">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1864,22 +1924,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>29.41</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5.7</v>
       </c>
       <c r="J40">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3318,22 +3381,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>40.63</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3420,22 +3486,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>81.25</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>18.75</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3452,22 +3521,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3484,22 +3556,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3516,22 +3591,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.6</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>34.38</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3548,22 +3626,25 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>84.09</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>15.91</v>
+      </c>
+      <c r="I11" s="2">
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>15.91</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3580,22 +3661,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>47.22</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>52.78</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3612,22 +3696,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>37.84</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>37.84</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3711,22 +3798,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>93.94</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>6.06</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3743,22 +3833,25 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3775,22 +3868,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3807,22 +3903,25 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>93.55</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>6.45</v>
+      </c>
+      <c r="I19" s="2">
+        <v>7.1</v>
       </c>
       <c r="J19">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>6.45</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3839,22 +3938,25 @@
         <v>28</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>17.86</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3871,22 +3973,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>17.65</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.5</v>
       </c>
       <c r="J21">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3903,22 +4008,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I22" s="2">
+        <v>8.4</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4145,22 +4253,25 @@
         <v>32</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5.9</v>
       </c>
       <c r="J29">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -4177,22 +4288,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>86.11</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>13.89</v>
+      </c>
+      <c r="I30" s="2">
+        <v>5.9</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4209,22 +4323,25 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>87.88</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>12.12</v>
+      </c>
+      <c r="I31" s="2">
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4436,22 +4553,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6.4</v>
       </c>
       <c r="J38">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4468,22 +4588,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>75.61</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>24.39</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.4</v>
       </c>
       <c r="J39">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4500,22 +4623,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>70.59</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>29.41</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5.7</v>
       </c>
       <c r="J40">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -1032,22 +1032,25 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1694,22 +1697,25 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1726,22 +1732,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>34.21</v>
+      </c>
+      <c r="I34" s="2">
+        <v>9.1</v>
       </c>
       <c r="J34">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1758,22 +1767,25 @@
         <v>35</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I35" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J35">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1790,22 +1802,25 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>29.17</v>
+      </c>
+      <c r="I36" s="2">
+        <v>8.1</v>
       </c>
       <c r="J36">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1822,22 +1837,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>48.39</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8.5</v>
       </c>
       <c r="J37">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3731,22 +3749,25 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>33.33</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -4393,22 +4414,25 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.2</v>
       </c>
       <c r="J33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4425,22 +4449,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>34.21</v>
+      </c>
+      <c r="I34" s="2">
+        <v>9.1</v>
       </c>
       <c r="J34">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4457,22 +4484,25 @@
         <v>35</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>77.14</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>22.86</v>
+      </c>
+      <c r="I35" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J35">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4489,22 +4519,25 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>29.17</v>
+      </c>
+      <c r="I36" s="2">
+        <v>8.1</v>
       </c>
       <c r="J36">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4521,22 +4554,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F37">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>51.61</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>48.39</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8.5</v>
       </c>
       <c r="J37">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="38" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -612,25 +612,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H2" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1239,28 +1239,28 @@
         <v>57</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="I20" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1277,25 +1277,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1382,25 +1382,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G24" s="1">
-        <v>78.79000000000001</v>
+        <v>93.94</v>
       </c>
       <c r="H24" s="1">
-        <v>21.21</v>
+        <v>6.06</v>
       </c>
       <c r="I24" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1417,25 +1417,25 @@
         <v>38</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1">
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5.26</v>
+      </c>
+      <c r="I25" s="2">
         <v>7</v>
       </c>
-      <c r="G25" s="1">
-        <v>81.58</v>
-      </c>
-      <c r="H25" s="1">
-        <v>18.42</v>
-      </c>
-      <c r="I25" s="2">
-        <v>7.3</v>
-      </c>
       <c r="J25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1452,25 +1452,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H26" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1487,25 +1487,25 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>83.87</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1522,25 +1522,25 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G28" s="1">
-        <v>56.25</v>
+        <v>81.25</v>
       </c>
       <c r="H28" s="1">
-        <v>43.75</v>
+        <v>18.75</v>
       </c>
       <c r="I28" s="2">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="J28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>43.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1659,19 +1659,19 @@
         <v>57</v>
       </c>
       <c r="D32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32">
         <v>32</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H32" s="1">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="I32" s="2">
         <v>7.4</v>
@@ -1764,28 +1764,28 @@
         <v>55</v>
       </c>
       <c r="D35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>27</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H35" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
       <c r="I35" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K35" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2602,13 +2602,13 @@
         <v>57</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
@@ -2617,7 +2617,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="1">
         <v>100</v>
@@ -2701,22 +2701,25 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2733,22 +2736,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>69.7</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>30.3</v>
+      </c>
+      <c r="I24" s="2">
+        <v>6.1</v>
       </c>
       <c r="J24">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2765,22 +2771,25 @@
         <v>38</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>34.21</v>
+      </c>
+      <c r="I25" s="2">
+        <v>6.5</v>
       </c>
       <c r="J25">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2797,22 +2806,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I26" s="2">
+        <v>6.8</v>
       </c>
       <c r="J26">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2829,22 +2841,25 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>19.35</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2861,22 +2876,25 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>37.5</v>
+      </c>
+      <c r="I28" s="2">
+        <v>6.2</v>
       </c>
       <c r="J28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2986,13 +3004,13 @@
         <v>57</v>
       </c>
       <c r="D32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
@@ -3001,7 +3019,7 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K32" s="1">
         <v>100</v>
@@ -3082,13 +3100,13 @@
         <v>55</v>
       </c>
       <c r="D35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
@@ -3097,7 +3115,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K35" s="1">
         <v>100</v>
@@ -3329,25 +3347,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>26.32</v>
+        <v>36.84</v>
       </c>
       <c r="H2" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
       <c r="I2" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1">
-        <v>73.68000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3956,28 +3974,28 @@
         <v>57</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20" s="1">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
       <c r="I20" s="2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3994,25 +4012,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
       <c r="I21" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>17.65</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4064,16 +4082,16 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="H23" s="1">
-        <v>29.17</v>
+        <v>25</v>
       </c>
       <c r="I23" s="2">
         <v>6.2</v>
@@ -4099,25 +4117,25 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F24">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1">
-        <v>78.79000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="H24" s="1">
-        <v>21.21</v>
+        <v>30.3</v>
       </c>
       <c r="I24" s="2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="J24">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>21.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -4134,25 +4152,25 @@
         <v>38</v>
       </c>
       <c r="E25">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G25" s="1">
-        <v>81.58</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H25" s="1">
-        <v>18.42</v>
+        <v>34.21</v>
       </c>
       <c r="I25" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -4169,25 +4187,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G26" s="1">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="H26" s="1">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="I26" s="2">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K26" s="1">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4204,25 +4222,25 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1">
-        <v>83.87</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>16.13</v>
+        <v>19.35</v>
       </c>
       <c r="I27" s="2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J27">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>16.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -4239,25 +4257,25 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G28" s="1">
-        <v>56.25</v>
+        <v>62.5</v>
       </c>
       <c r="H28" s="1">
-        <v>43.75</v>
+        <v>37.5</v>
       </c>
       <c r="I28" s="2">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="J28">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>43.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -4376,19 +4394,19 @@
         <v>57</v>
       </c>
       <c r="D32">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E32">
         <v>32</v>
       </c>
       <c r="F32">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" s="1">
-        <v>86.48999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="H32" s="1">
-        <v>13.51</v>
+        <v>11.11</v>
       </c>
       <c r="I32" s="2">
         <v>7.4</v>
@@ -4481,28 +4499,28 @@
         <v>55</v>
       </c>
       <c r="D35">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E35">
         <v>27</v>
       </c>
       <c r="F35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35" s="1">
-        <v>77.14</v>
+        <v>79.41</v>
       </c>
       <c r="H35" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
       <c r="I35" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K35" s="1">
-        <v>22.86</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="36" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -624,13 +624,13 @@
         <v>63.16</v>
       </c>
       <c r="I2" s="2">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -682,25 +682,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4" s="1">
-        <v>40.63</v>
+        <v>37.5</v>
       </c>
       <c r="I4" s="2">
         <v>7.2</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -732,10 +732,10 @@
         <v>7.4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -799,13 +799,13 @@
         <v>18.75</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -822,25 +822,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8" s="1">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>22.73</v>
+        <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -869,13 +869,13 @@
         <v>10.81</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -904,13 +904,13 @@
         <v>34.38</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -939,13 +939,13 @@
         <v>15.91</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -962,25 +962,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H12" s="1">
-        <v>52.78</v>
+        <v>50</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -997,25 +997,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>37.84</v>
+        <v>32.43</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="J13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>37.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1032,25 +1032,25 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>66.67</v>
+        <v>85.19</v>
       </c>
       <c r="H14" s="1">
-        <v>33.33</v>
+        <v>14.81</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1102,25 +1102,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H16" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
       <c r="I16" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1137,25 +1137,25 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H17" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1172,25 +1172,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H18" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="2">
         <v>8.4</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1219,13 +1219,13 @@
         <v>6.45</v>
       </c>
       <c r="I19" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1242,25 +1242,25 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>17.24</v>
+        <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1277,25 +1277,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>14.71</v>
+        <v>8.82</v>
       </c>
       <c r="I21" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1312,25 +1312,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>26.32</v>
+        <v>5.26</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1732,25 +1732,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H34" s="1">
-        <v>34.21</v>
+        <v>21.05</v>
       </c>
       <c r="I34" s="2">
-        <v>9.1</v>
+        <v>7.8</v>
       </c>
       <c r="J34">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1767,25 +1767,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G35" s="1">
-        <v>79.41</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H35" s="1">
-        <v>20.59</v>
+        <v>14.71</v>
       </c>
       <c r="I35" s="2">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1802,25 +1802,25 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1">
-        <v>70.83</v>
+        <v>79.17</v>
       </c>
       <c r="H36" s="1">
-        <v>29.17</v>
+        <v>20.83</v>
       </c>
       <c r="I36" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>29.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1837,25 +1837,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>48.39</v>
+        <v>32.26</v>
       </c>
       <c r="I37" s="2">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1884,13 +1884,13 @@
         <v>14.29</v>
       </c>
       <c r="I38" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -1907,25 +1907,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G39" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
       <c r="I39" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K39" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2029,22 +2029,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>47.37</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>52.63</v>
+      </c>
+      <c r="I2" s="2">
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2061,22 +2064,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>29.03</v>
+      </c>
+      <c r="I3" s="2">
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2093,22 +2099,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>59.38</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>40.63</v>
+      </c>
+      <c r="I4" s="2">
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2125,22 +2134,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2157,22 +2169,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I6" s="2">
+        <v>6.8</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2189,22 +2204,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I7" s="2">
+        <v>6.1</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2221,22 +2239,25 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I8" s="2">
+        <v>6.9</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2253,22 +2274,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>83.78</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>16.22</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2285,22 +2309,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>28.13</v>
+      </c>
+      <c r="I10" s="2">
+        <v>6.4</v>
       </c>
       <c r="J10">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2317,22 +2344,25 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>86.36</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>13.64</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.5</v>
       </c>
       <c r="J11">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2349,22 +2379,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.2</v>
       </c>
       <c r="J12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2381,22 +2414,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>32.43</v>
+      </c>
+      <c r="I13" s="2">
+        <v>6.5</v>
       </c>
       <c r="J13">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2413,22 +2449,25 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.6</v>
       </c>
       <c r="J14">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2445,22 +2484,25 @@
         <v>22</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J15">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2477,22 +2519,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F16">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2509,22 +2554,25 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>89.47</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>10.53</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2541,22 +2589,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I18" s="2">
+        <v>9.1</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2573,22 +2624,25 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F19">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>70.97</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>29.03</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6.3</v>
       </c>
       <c r="J19">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2605,22 +2659,25 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>6.9</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.8</v>
       </c>
       <c r="J20">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2637,22 +2694,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>8.82</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.6</v>
       </c>
       <c r="J21">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2669,22 +2729,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2911,22 +2974,25 @@
         <v>32</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>65.63</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>34.38</v>
+      </c>
+      <c r="I29" s="2">
+        <v>5.8</v>
       </c>
       <c r="J29">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2943,22 +3009,25 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H30" s="1">
-        <v>100</v>
+        <v>41.67</v>
+      </c>
+      <c r="I30" s="2">
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3007,22 +3076,25 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F32">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H32" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I32" s="2">
+        <v>6.5</v>
       </c>
       <c r="J32">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K32" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3071,22 +3143,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8.4</v>
       </c>
       <c r="J34">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="K34" s="1">
-        <v>100</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3103,22 +3178,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F35">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H35" s="1">
-        <v>100</v>
+        <v>11.76</v>
+      </c>
+      <c r="I35" s="2">
+        <v>9.1</v>
       </c>
       <c r="J35">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="K35" s="1">
-        <v>100</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3135,22 +3213,25 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H36" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7.9</v>
       </c>
       <c r="J36">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K36" s="1">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3167,22 +3248,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F37">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H37" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J37">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K37" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3199,22 +3283,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F38">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>60.71</v>
       </c>
       <c r="H38" s="1">
-        <v>100</v>
+        <v>39.29</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6.2</v>
       </c>
       <c r="J38">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="K38" s="1">
-        <v>100</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3231,22 +3318,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>41.46</v>
       </c>
       <c r="H39" s="1">
-        <v>100</v>
+        <v>58.54</v>
+      </c>
+      <c r="I39" s="2">
+        <v>6.2</v>
       </c>
       <c r="J39">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="K39" s="1">
-        <v>100</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3263,22 +3353,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G40" s="1">
-        <v>0</v>
+        <v>58.82</v>
       </c>
       <c r="H40" s="1">
-        <v>100</v>
+        <v>41.18</v>
+      </c>
+      <c r="I40" s="2">
+        <v>5.9</v>
       </c>
       <c r="J40">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K40" s="1">
-        <v>100</v>
+        <v>29.41</v>
       </c>
     </row>
   </sheetData>
@@ -3347,25 +3440,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>36.84</v>
+        <v>47.37</v>
       </c>
       <c r="H2" s="1">
-        <v>63.16</v>
+        <v>52.63</v>
       </c>
       <c r="I2" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K2" s="1">
-        <v>63.16</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3382,19 +3475,19 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G3" s="1">
-        <v>77.42</v>
+        <v>70.97</v>
       </c>
       <c r="H3" s="1">
-        <v>22.58</v>
+        <v>29.03</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -3417,25 +3510,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4" s="1">
-        <v>40.63</v>
+        <v>37.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3452,25 +3545,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>68.75</v>
+        <v>65.63</v>
       </c>
       <c r="H5" s="1">
-        <v>31.25</v>
+        <v>34.38</v>
       </c>
       <c r="I5" s="2">
         <v>7.4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3499,7 +3592,7 @@
         <v>27.27</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -3522,25 +3615,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>81.25</v>
+        <v>78.13</v>
       </c>
       <c r="H7" s="1">
-        <v>18.75</v>
+        <v>21.88</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3569,13 +3662,13 @@
         <v>22.73</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3592,25 +3685,25 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>89.19</v>
+        <v>83.78</v>
       </c>
       <c r="H9" s="1">
-        <v>10.81</v>
+        <v>16.22</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3627,25 +3720,25 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H10" s="1">
-        <v>34.38</v>
+        <v>28.13</v>
       </c>
       <c r="I10" s="2">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>34.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3662,25 +3755,25 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>84.09</v>
+        <v>86.36</v>
       </c>
       <c r="H11" s="1">
-        <v>15.91</v>
+        <v>13.64</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>15.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3697,25 +3790,25 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="1">
-        <v>47.22</v>
+        <v>50</v>
       </c>
       <c r="H12" s="1">
-        <v>52.78</v>
+        <v>50</v>
       </c>
       <c r="I12" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -3732,25 +3825,25 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
-        <v>62.16</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>37.84</v>
+        <v>32.43</v>
       </c>
       <c r="I13" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J13">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>37.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3767,25 +3860,25 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H14" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I14" s="2">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -3814,7 +3907,7 @@
         <v>9.09</v>
       </c>
       <c r="I15" s="2">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -3837,25 +3930,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="1">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H16" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
       <c r="I16" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>6.06</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3872,25 +3965,25 @@
         <v>19</v>
       </c>
       <c r="E17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H17" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3907,25 +4000,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H18" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K18" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3942,25 +4035,25 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>93.55</v>
+        <v>70.97</v>
       </c>
       <c r="H19" s="1">
-        <v>6.45</v>
+        <v>29.03</v>
       </c>
       <c r="I19" s="2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3977,25 +4070,25 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H20" s="1">
-        <v>17.24</v>
+        <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -4012,25 +4105,25 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H21" s="1">
-        <v>14.71</v>
+        <v>8.82</v>
       </c>
       <c r="I21" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -4047,25 +4140,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>26.32</v>
+        <v>5.26</v>
       </c>
       <c r="I22" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -4292,19 +4385,19 @@
         <v>32</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G29" s="1">
-        <v>87.5</v>
+        <v>65.63</v>
       </c>
       <c r="H29" s="1">
-        <v>12.5</v>
+        <v>34.38</v>
       </c>
       <c r="I29" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4327,16 +4420,16 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F30">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G30" s="1">
-        <v>86.11</v>
+        <v>58.33</v>
       </c>
       <c r="H30" s="1">
-        <v>13.89</v>
+        <v>41.67</v>
       </c>
       <c r="I30" s="2">
         <v>5.9</v>
@@ -4397,19 +4490,19 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G32" s="1">
-        <v>88.89</v>
+        <v>77.78</v>
       </c>
       <c r="H32" s="1">
-        <v>11.11</v>
+        <v>22.22</v>
       </c>
       <c r="I32" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4467,25 +4560,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>65.79000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H34" s="1">
-        <v>34.21</v>
+        <v>21.05</v>
       </c>
       <c r="I34" s="2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>34.21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -4502,25 +4595,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F35">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H35" s="1">
-        <v>20.59</v>
+        <v>5.88</v>
       </c>
       <c r="I35" s="2">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -4537,25 +4630,25 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G36" s="1">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H36" s="1">
-        <v>29.17</v>
+        <v>8.33</v>
       </c>
       <c r="I36" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J36">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>29.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -4572,25 +4665,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F37">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1">
-        <v>51.61</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H37" s="1">
-        <v>48.39</v>
+        <v>32.26</v>
       </c>
       <c r="I37" s="2">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="J37">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>48.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -4607,25 +4700,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>85.70999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>14.29</v>
+        <v>21.43</v>
       </c>
       <c r="I38" s="2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K38" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -4642,25 +4735,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G39" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H39" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
       <c r="I39" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K39" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="40" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -1709,13 +1709,13 @@
         <v>50</v>
       </c>
       <c r="I33" s="2">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3044,22 +3044,25 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H31" s="1">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I31" s="2">
+        <v>5.7</v>
       </c>
       <c r="J31">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3111,22 +3114,25 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H33" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I33" s="2">
+        <v>7.8</v>
       </c>
       <c r="J33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K33" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4455,19 +4461,19 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1">
-        <v>87.88</v>
+        <v>63.64</v>
       </c>
       <c r="H31" s="1">
-        <v>12.12</v>
+        <v>36.36</v>
       </c>
       <c r="I31" s="2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -4525,25 +4531,25 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H33" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -1102,25 +1102,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
         <v>9.4</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1464,13 +1464,13 @@
         <v>4.17</v>
       </c>
       <c r="I26" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1872,25 +1872,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G38" s="1">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H38" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
       <c r="I38" s="2">
         <v>6.3</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2519,25 +2519,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2671,7 +2671,7 @@
         <v>6.9</v>
       </c>
       <c r="I20" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2869,25 +2869,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="1">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="H26" s="1">
-        <v>25</v>
+        <v>20.83</v>
       </c>
       <c r="I26" s="2">
         <v>6.8</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3114,25 +3114,25 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G33" s="1">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="H33" s="1">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I33" s="2">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="J33">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -3149,25 +3149,25 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>73.68000000000001</v>
+        <v>78.95</v>
       </c>
       <c r="H34" s="1">
-        <v>26.32</v>
+        <v>21.05</v>
       </c>
       <c r="I34" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J34">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -3184,25 +3184,25 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H35" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I35" s="2">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1">
-        <v>8.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -3231,13 +3231,13 @@
         <v>8.33</v>
       </c>
       <c r="I36" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -3254,25 +3254,25 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F37">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G37" s="1">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H37" s="1">
-        <v>35.48</v>
+        <v>22.58</v>
       </c>
       <c r="I37" s="2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J37">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -3289,25 +3289,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G38" s="1">
-        <v>60.71</v>
+        <v>82.14</v>
       </c>
       <c r="H38" s="1">
-        <v>39.29</v>
+        <v>17.86</v>
       </c>
       <c r="I38" s="2">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J38">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K38" s="1">
-        <v>32.14</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3359,25 +3359,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1">
-        <v>58.82</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="H40" s="1">
-        <v>41.18</v>
+        <v>35.29</v>
       </c>
       <c r="I40" s="2">
         <v>5.9</v>
       </c>
       <c r="J40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>29.41</v>
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -3621,19 +3621,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3656,19 +3656,19 @@
         <v>44</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>77.27</v>
+        <v>88.64</v>
       </c>
       <c r="H8" s="1">
-        <v>22.73</v>
+        <v>11.36</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -3691,19 +3691,19 @@
         <v>37</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>16.22</v>
+        <v>13.51</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -3726,19 +3726,19 @@
         <v>32</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>71.88</v>
+        <v>93.75</v>
       </c>
       <c r="H10" s="1">
-        <v>28.13</v>
+        <v>6.25</v>
       </c>
       <c r="I10" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -3761,19 +3761,19 @@
         <v>44</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>86.36</v>
+        <v>97.73</v>
       </c>
       <c r="H11" s="1">
-        <v>13.64</v>
+        <v>2.27</v>
       </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -3796,19 +3796,19 @@
         <v>36</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="H12" s="1">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="I12" s="2">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3831,16 +3831,16 @@
         <v>37</v>
       </c>
       <c r="E13">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>67.56999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="H13" s="1">
-        <v>32.43</v>
+        <v>10.81</v>
       </c>
       <c r="I13" s="2">
         <v>6.5</v>
@@ -3866,19 +3866,19 @@
         <v>27</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>77.78</v>
+        <v>96.3</v>
       </c>
       <c r="H14" s="1">
-        <v>22.22</v>
+        <v>3.7</v>
       </c>
       <c r="I14" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3936,25 +3936,25 @@
         <v>33</v>
       </c>
       <c r="E16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>3.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -4041,16 +4041,16 @@
         <v>31</v>
       </c>
       <c r="E19">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H19" s="1">
-        <v>29.03</v>
+        <v>22.58</v>
       </c>
       <c r="I19" s="2">
         <v>6.6</v>
@@ -4076,19 +4076,19 @@
         <v>29</v>
       </c>
       <c r="E20">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G20" s="1">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H20" s="1">
-        <v>6.9</v>
+        <v>10.34</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4111,19 +4111,19 @@
         <v>34</v>
       </c>
       <c r="E21">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H21" s="1">
-        <v>8.82</v>
+        <v>2.94</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>5.26</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -4181,19 +4181,19 @@
         <v>24</v>
       </c>
       <c r="E23">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>75</v>
+        <v>91.67</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>8.33</v>
       </c>
       <c r="I23" s="2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -4216,19 +4216,19 @@
         <v>33</v>
       </c>
       <c r="E24">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G24" s="1">
-        <v>69.7</v>
+        <v>87.88</v>
       </c>
       <c r="H24" s="1">
-        <v>30.3</v>
+        <v>12.12</v>
       </c>
       <c r="I24" s="2">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -4251,19 +4251,19 @@
         <v>38</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H25" s="1">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
       <c r="I25" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -4286,25 +4286,25 @@
         <v>24</v>
       </c>
       <c r="E26">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="H26" s="1">
-        <v>25</v>
+        <v>4.17</v>
       </c>
       <c r="I26" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -4321,19 +4321,19 @@
         <v>31</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>80.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1">
-        <v>19.35</v>
+        <v>0</v>
       </c>
       <c r="I27" s="2">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -4356,16 +4356,16 @@
         <v>32</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F28">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G28" s="1">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H28" s="1">
-        <v>37.5</v>
+        <v>15.63</v>
       </c>
       <c r="I28" s="2">
         <v>6.3</v>
@@ -4531,19 +4531,19 @@
         <v>20</v>
       </c>
       <c r="E33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G33" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H33" s="1">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -4601,19 +4601,19 @@
         <v>34</v>
       </c>
       <c r="E35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" s="1">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H35" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I35" s="2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -4636,16 +4636,16 @@
         <v>24</v>
       </c>
       <c r="E36">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H36" s="1">
-        <v>8.33</v>
+        <v>4.17</v>
       </c>
       <c r="I36" s="2">
         <v>7.7</v>
@@ -4671,19 +4671,19 @@
         <v>31</v>
       </c>
       <c r="E37">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F37">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1">
-        <v>67.73999999999999</v>
+        <v>100</v>
       </c>
       <c r="H37" s="1">
-        <v>32.26</v>
+        <v>0</v>
       </c>
       <c r="I37" s="2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -4706,25 +4706,25 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F38">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G38" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H38" s="1">
-        <v>21.43</v>
+        <v>14.29</v>
       </c>
       <c r="I38" s="2">
         <v>6.2</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>7.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -4426,16 +4426,16 @@
         <v>36</v>
       </c>
       <c r="E30">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1">
-        <v>58.33</v>
+        <v>72.22</v>
       </c>
       <c r="H30" s="1">
-        <v>41.67</v>
+        <v>27.78</v>
       </c>
       <c r="I30" s="2">
         <v>5.9</v>
@@ -4566,19 +4566,19 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G34" s="1">
-        <v>78.95</v>
+        <v>86.84</v>
       </c>
       <c r="H34" s="1">
-        <v>21.05</v>
+        <v>13.16</v>
       </c>
       <c r="I34" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Matemáticas - Estadisticos 20212.xlsx
+++ b/academias/Matemáticas - Estadisticos 20212.xlsx
@@ -612,25 +612,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1">
-        <v>36.84</v>
+        <v>42.11</v>
       </c>
       <c r="H2" s="1">
-        <v>63.16</v>
+        <v>57.89</v>
       </c>
       <c r="I2" s="2">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -659,13 +659,13 @@
         <v>22.58</v>
       </c>
       <c r="I3" s="2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -694,13 +694,13 @@
         <v>37.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -729,13 +729,13 @@
         <v>31.25</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -764,13 +764,13 @@
         <v>27.27</v>
       </c>
       <c r="I6" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1067,25 +1067,25 @@
         <v>22</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1149,13 +1149,13 @@
         <v>10.53</v>
       </c>
       <c r="I17" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1172,25 +1172,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H18" s="1">
-        <v>12.5</v>
+        <v>3.13</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1907,25 +1907,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G39" s="1">
-        <v>82.93000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H39" s="1">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
       <c r="I39" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2029,25 +2029,25 @@
         <v>19</v>
       </c>
       <c r="E2">
+        <v>10</v>
+      </c>
+      <c r="F2">
         <v>9</v>
       </c>
-      <c r="F2">
-        <v>10</v>
-      </c>
       <c r="G2" s="1">
+        <v>52.63</v>
+      </c>
+      <c r="H2" s="1">
         <v>47.37</v>
       </c>
-      <c r="H2" s="1">
-        <v>52.63</v>
-      </c>
       <c r="I2" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2076,13 +2076,13 @@
         <v>29.03</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2099,25 +2099,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="H4" s="1">
-        <v>40.63</v>
+        <v>37.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2146,13 +2146,13 @@
         <v>34.38</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2181,13 +2181,13 @@
         <v>27.27</v>
       </c>
       <c r="I6" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2484,25 +2484,25 @@
         <v>22</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2566,13 +2566,13 @@
         <v>10.53</v>
       </c>
       <c r="I17" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2589,25 +2589,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>78.13</v>
+        <v>93.75</v>
       </c>
       <c r="H18" s="1">
-        <v>21.88</v>
+        <v>6.25</v>
       </c>
       <c r="I18" s="2">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3091,13 +3091,13 @@
         <v>25</v>
       </c>
       <c r="I32" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3304,10 +3304,10 @@
         <v>6.1</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -3324,25 +3324,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F39">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>41.46</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H39" s="1">
-        <v>58.54</v>
+        <v>19.51</v>
       </c>
       <c r="I39" s="2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J39">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>58.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -3359,25 +3359,25 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" s="1">
-        <v>64.70999999999999</v>
+        <v>70.59</v>
       </c>
       <c r="H40" s="1">
-        <v>35.29</v>
+        <v>29.41</v>
       </c>
       <c r="I40" s="2">
         <v>5.9</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3446,25 +3446,25 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H2" s="1">
-        <v>52.63</v>
+        <v>21.05</v>
       </c>
       <c r="I2" s="2">
         <v>6.1</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -3481,25 +3481,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>70.97</v>
+        <v>93.55</v>
       </c>
       <c r="H3" s="1">
-        <v>29.03</v>
+        <v>6.45</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -3516,25 +3516,25 @@
         <v>32</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="H4" s="1">
-        <v>37.5</v>
+        <v>12.5</v>
       </c>
       <c r="I4" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3551,25 +3551,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>65.63</v>
+        <v>90.63</v>
       </c>
       <c r="H5" s="1">
-        <v>34.38</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3586,25 +3586,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1">
-        <v>72.73</v>
+        <v>87.88</v>
       </c>
       <c r="H6" s="1">
-        <v>27.27</v>
+        <v>12.12</v>
       </c>
       <c r="I6" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3901,25 +3901,25 @@
         <v>22</v>
       </c>
       <c r="E15">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3948,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -3983,13 +3983,13 @@
         <v>10.53</v>
       </c>
       <c r="I17" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>10.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -4006,25 +4006,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H18" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -4391,19 +4391,19 @@
         <v>32</v>
       </c>
       <c r="E29">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G29" s="1">
-        <v>65.63</v>
+        <v>71.88</v>
       </c>
       <c r="H29" s="1">
-        <v>34.38</v>
+        <v>28.13</v>
       </c>
       <c r="I29" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -4461,16 +4461,16 @@
         <v>33</v>
       </c>
       <c r="E31">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G31" s="1">
-        <v>63.64</v>
+        <v>72.73</v>
       </c>
       <c r="H31" s="1">
-        <v>36.36</v>
+        <v>27.27</v>
       </c>
       <c r="I31" s="2">
         <v>5.8</v>
@@ -4496,19 +4496,19 @@
         <v>36</v>
       </c>
       <c r="E32">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1">
-        <v>77.78</v>
+        <v>91.67</v>
       </c>
       <c r="H32" s="1">
-        <v>22.22</v>
+        <v>8.33</v>
       </c>
       <c r="I32" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -4566,16 +4566,16 @@
         <v>38</v>
       </c>
       <c r="E34">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1">
-        <v>86.84</v>
+        <v>92.11</v>
       </c>
       <c r="H34" s="1">
-        <v>13.16</v>
+        <v>7.89</v>
       </c>
       <c r="I34" s="2">
         <v>8.1</v>
@@ -4706,19 +4706,19 @@
         <v>28</v>
       </c>
       <c r="E38">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H38" s="1">
-        <v>14.29</v>
+        <v>3.57</v>
       </c>
       <c r="I38" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -4741,25 +4741,25 @@
         <v>41</v>
       </c>
       <c r="E39">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>82.93000000000001</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="H39" s="1">
-        <v>17.07</v>
+        <v>19.51</v>
       </c>
       <c r="I39" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J39">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K39" s="1">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -4776,19 +4776,19 @@
         <v>17</v>
       </c>
       <c r="E40">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>70.59</v>
+        <v>100</v>
       </c>
       <c r="H40" s="1">
-        <v>29.41</v>
+        <v>0</v>
       </c>
       <c r="I40" s="2">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J40">
         <v>0</v>
